--- a/artfynd/A 28173-2026 artfynd.xlsx
+++ b/artfynd/A 28173-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135999555</v>
+        <v>136032180</v>
       </c>
       <c r="B3" t="n">
-        <v>92071</v>
+        <v>92321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,40 +808,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kyrktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556613</v>
+        <v>556570</v>
       </c>
       <c r="R3" t="n">
-        <v>6723985</v>
+        <v>6724021</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På levande stående tall</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,31 +886,30 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135999555</t>
+          <t>https://artportalen.se/Sighting/136032180</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135999556</v>
+        <v>135999555</v>
       </c>
       <c r="B4" t="n">
         <v>92071</v>
@@ -946,24 +937,23 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kyrktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556659</v>
+        <v>556613</v>
       </c>
       <c r="R4" t="n">
-        <v>6723942</v>
+        <v>6723985</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,12 +992,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en stormfälld tall</t>
+          <t>På levande stående tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,6 +1006,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1033,54 +1024,58 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135999556</t>
+          <t>https://artportalen.se/Sighting/135999555</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135999551</v>
+        <v>135999556</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>92071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kyrktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556553</v>
+        <v>556659</v>
       </c>
       <c r="R5" t="n">
-        <v>6724039</v>
+        <v>6723942</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,12 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På stående levande granar</t>
+          <t>På en stormfälld tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,13 +1145,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135999551</t>
+          <t>https://artportalen.se/Sighting/135999556</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135999552</v>
+        <v>135999551</v>
       </c>
       <c r="B6" t="n">
         <v>79441</v>
@@ -1191,13 +1186,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556548</v>
+        <v>556553</v>
       </c>
       <c r="R6" t="n">
-        <v>6724023</v>
+        <v>6724039</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1267,13 +1262,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135999552</t>
+          <t>https://artportalen.se/Sighting/135999551</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135999557</v>
+        <v>135999552</v>
       </c>
       <c r="B7" t="n">
         <v>79441</v>
@@ -1308,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556658</v>
+        <v>556548</v>
       </c>
       <c r="R7" t="n">
-        <v>6723939</v>
+        <v>6724023</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,12 +1348,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På stormfälld tall</t>
+          <t>På stående levande granar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,59 +1379,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135999557</t>
+          <t>https://artportalen.se/Sighting/135999552</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135999554</v>
+        <v>135999557</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>79441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kyrktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556583</v>
+        <v>556658</v>
       </c>
       <c r="R8" t="n">
-        <v>6723986</v>
+        <v>6723939</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1465,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1475,12 +1465,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på nylåga</t>
+          <t>På stormfälld tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,6 +1495,485 @@
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135999557</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136032178</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kyrktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>556557</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6724054</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ganska rikligt på vindfällen</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136032178</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136032179</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kyrktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>556567</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6724029</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På stormfällda träd.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136032179</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136032183</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kyrktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>556688</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6723855</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På stående, levande gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136032183</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135999554</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kyrktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>556583</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6723986</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på nylåga</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135999554</t>
         </is>
@@ -1519,6 +1988,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28173-2026 artfynd.xlsx
+++ b/artfynd/A 28173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135999553</v>
       </c>
       <c r="B2" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136032180</v>
       </c>
       <c r="B3" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135999555</v>
       </c>
       <c r="B4" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135999556</v>
       </c>
       <c r="B5" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>135999551</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>135999552</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>135999557</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136032178</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136032179</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>136032183</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>135999554</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28173-2026 artfynd.xlsx
+++ b/artfynd/A 28173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135999553</v>
       </c>
       <c r="B2" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136032180</v>
       </c>
       <c r="B3" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135999555</v>
       </c>
       <c r="B4" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135999556</v>
       </c>
       <c r="B5" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>135999551</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>135999552</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>135999557</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136032178</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136032179</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>136032183</v>
       </c>
       <c r="B11" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 28173-2026 artfynd.xlsx
+++ b/artfynd/A 28173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135999553</v>
       </c>
       <c r="B2" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136032180</v>
       </c>
       <c r="B3" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135999555</v>
       </c>
       <c r="B4" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135999556</v>
       </c>
       <c r="B5" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28173-2026 artfynd.xlsx
+++ b/artfynd/A 28173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135999553</v>
       </c>
       <c r="B2" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136032180</v>
       </c>
       <c r="B3" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135999555</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135999556</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>135999551</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>135999552</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>135999557</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136032178</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136032179</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>136032183</v>
       </c>
       <c r="B11" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>135999554</v>
       </c>
       <c r="B12" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28173-2026 artfynd.xlsx
+++ b/artfynd/A 28173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135999553</v>
       </c>
       <c r="B2" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136032180</v>
       </c>
       <c r="B3" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135999555</v>
       </c>
       <c r="B4" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135999556</v>
       </c>
       <c r="B5" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>135999551</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>135999552</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>135999557</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136032178</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136032179</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>136032183</v>
       </c>
       <c r="B11" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>135999554</v>
       </c>
       <c r="B12" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28173-2026 artfynd.xlsx
+++ b/artfynd/A 28173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135999553</v>
       </c>
       <c r="B2" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136032180</v>
       </c>
       <c r="B3" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135999555</v>
       </c>
       <c r="B4" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135999556</v>
       </c>
       <c r="B5" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>135999551</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>135999552</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>135999557</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136032178</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136032179</v>
       </c>
       <c r="B10" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>136032183</v>
       </c>
       <c r="B11" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>135999554</v>
       </c>
       <c r="B12" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28173-2026 artfynd.xlsx
+++ b/artfynd/A 28173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135999553</v>
       </c>
       <c r="B2" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136032180</v>
       </c>
       <c r="B3" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135999555</v>
       </c>
       <c r="B4" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135999556</v>
       </c>
       <c r="B5" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>135999551</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>135999552</v>
       </c>
       <c r="B7" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>135999557</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136032178</v>
       </c>
       <c r="B9" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136032179</v>
       </c>
       <c r="B10" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>136032183</v>
       </c>
       <c r="B11" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 28173-2026 artfynd.xlsx
+++ b/artfynd/A 28173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135999553</v>
       </c>
       <c r="B2" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136032180</v>
       </c>
       <c r="B3" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135999555</v>
       </c>
       <c r="B4" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135999556</v>
       </c>
       <c r="B5" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>135999551</v>
       </c>
       <c r="B6" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>135999552</v>
       </c>
       <c r="B7" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>135999557</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136032178</v>
       </c>
       <c r="B9" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136032179</v>
       </c>
       <c r="B10" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>136032183</v>
       </c>
       <c r="B11" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>135999554</v>
       </c>
       <c r="B12" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28173-2026 artfynd.xlsx
+++ b/artfynd/A 28173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135999553</v>
       </c>
       <c r="B2" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136032180</v>
       </c>
       <c r="B3" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135999555</v>
       </c>
       <c r="B4" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135999556</v>
       </c>
       <c r="B5" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28173-2026 artfynd.xlsx
+++ b/artfynd/A 28173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135999553</v>
       </c>
       <c r="B2" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136032180</v>
       </c>
       <c r="B3" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135999555</v>
       </c>
       <c r="B4" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135999556</v>
       </c>
       <c r="B5" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>135999551</v>
       </c>
       <c r="B6" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>135999552</v>
       </c>
       <c r="B7" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>135999557</v>
       </c>
       <c r="B8" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136032178</v>
       </c>
       <c r="B9" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136032179</v>
       </c>
       <c r="B10" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>136032183</v>
       </c>
       <c r="B11" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>135999554</v>
       </c>
       <c r="B12" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 28173-2026 artfynd.xlsx
+++ b/artfynd/A 28173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135999553</v>
       </c>
       <c r="B2" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136032180</v>
       </c>
       <c r="B3" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135999555</v>
       </c>
       <c r="B4" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135999556</v>
       </c>
       <c r="B5" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>135999551</v>
       </c>
       <c r="B6" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>135999552</v>
       </c>
       <c r="B7" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>135999557</v>
       </c>
       <c r="B8" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136032178</v>
       </c>
       <c r="B9" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136032179</v>
       </c>
       <c r="B10" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>136032183</v>
       </c>
       <c r="B11" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
